--- a/Team-Data/2014-15/2-26-2014-15.xlsx
+++ b/Team-Data/2014-15/2-26-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>6.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -751,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
         <v>12</v>
@@ -775,7 +842,7 @@
         <v>13</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>22</v>
@@ -933,7 +1000,7 @@
         <v>22</v>
       </c>
       <c r="AH3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
@@ -984,10 +1051,10 @@
         <v>29</v>
       </c>
       <c r="AY3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1115,7 +1182,7 @@
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
         <v>22</v>
@@ -1154,7 +1221,7 @@
         <v>21</v>
       </c>
       <c r="AU4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
         <v>14</v>
@@ -1166,13 +1233,13 @@
         <v>22</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1333,10 +1400,10 @@
         <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -1467,25 +1534,25 @@
         <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
         <v>5</v>
       </c>
       <c r="AI6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK6" t="n">
         <v>21</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n">
         <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>0.627</v>
+        <v>0.621</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J7" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>0.458</v>
@@ -1604,31 +1671,31 @@
         <v>0.355</v>
       </c>
       <c r="O7" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="P7" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.754</v>
+        <v>0.752</v>
       </c>
       <c r="R7" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="T7" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="U7" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X7" t="n">
         <v>4.1</v>
@@ -1643,16 +1710,16 @@
         <v>20.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>102.7</v>
+        <v>102.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1661,16 +1728,16 @@
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ7" t="n">
         <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>8</v>
@@ -1682,19 +1749,19 @@
         <v>11</v>
       </c>
       <c r="AO7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
         <v>17</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT7" t="n">
         <v>19</v>
@@ -1706,7 +1773,7 @@
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
         <v>39</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>0.661</v>
+        <v>0.65</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,7 +1838,7 @@
         <v>39.7</v>
       </c>
       <c r="J8" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K8" t="n">
         <v>0.463</v>
@@ -1780,10 +1847,10 @@
         <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O8" t="n">
         <v>16.6</v>
@@ -1792,22 +1859,22 @@
         <v>21.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R8" t="n">
         <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T8" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V8" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W8" t="n">
         <v>8.199999999999999</v>
@@ -1819,7 +1886,7 @@
         <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA8" t="n">
         <v>21.7</v>
@@ -1828,7 +1895,7 @@
         <v>105.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1837,10 +1904,10 @@
         <v>4</v>
       </c>
       <c r="AF8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG8" t="n">
         <v>6</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>5</v>
       </c>
       <c r="AH8" t="n">
         <v>14</v>
@@ -1849,13 +1916,13 @@
         <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM8" t="n">
         <v>4</v>
@@ -1873,10 +1940,10 @@
         <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
@@ -1891,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
         <v>3</v>
@@ -1906,7 +1973,7 @@
         <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2025,7 +2092,7 @@
         <v>25</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>18</v>
@@ -2046,10 +2113,10 @@
         <v>29</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>24</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>18</v>
@@ -2264,7 +2331,7 @@
         <v>7</v>
       </c>
       <c r="BA10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
         <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2317,10 +2384,10 @@
         <v>41.7</v>
       </c>
       <c r="J11" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="K11" t="n">
-        <v>0.478</v>
+        <v>0.479</v>
       </c>
       <c r="L11" t="n">
         <v>10.5</v>
@@ -2329,16 +2396,16 @@
         <v>27.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.388</v>
+        <v>0.389</v>
       </c>
       <c r="O11" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="P11" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.77</v>
+        <v>0.774</v>
       </c>
       <c r="R11" t="n">
         <v>10.3</v>
@@ -2350,7 +2417,7 @@
         <v>44.7</v>
       </c>
       <c r="U11" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="V11" t="n">
         <v>14.6</v>
@@ -2362,22 +2429,22 @@
         <v>6</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA11" t="n">
         <v>19.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>110.2</v>
+        <v>110.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2410,13 +2477,13 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="n">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.679</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J12" t="n">
-        <v>84.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.438</v>
@@ -2508,19 +2575,19 @@
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O12" t="n">
-        <v>17.6</v>
+        <v>17.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.6</v>
+        <v>25.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.716</v>
+        <v>0.715</v>
       </c>
       <c r="R12" t="n">
         <v>12.3</v>
@@ -2529,16 +2596,16 @@
         <v>31.6</v>
       </c>
       <c r="T12" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U12" t="n">
         <v>21.8</v>
       </c>
       <c r="V12" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="W12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X12" t="n">
         <v>4.8</v>
@@ -2547,22 +2614,22 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
@@ -2571,10 +2638,10 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ12" t="n">
         <v>12</v>
@@ -2595,7 +2662,7 @@
         <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2607,7 +2674,7 @@
         <v>23</v>
       </c>
       <c r="AT12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
         <v>13</v>
@@ -2622,13 +2689,13 @@
         <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>18</v>
@@ -2753,13 +2820,13 @@
         <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
@@ -2777,10 +2844,10 @@
         <v>24</v>
       </c>
       <c r="AP13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
         <v>20</v>
@@ -2795,7 +2862,7 @@
         <v>18</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -2923,13 +2990,13 @@
         <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
         <v>8</v>
@@ -2941,7 +3008,7 @@
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
@@ -2962,7 +3029,7 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>0.273</v>
+        <v>0.268</v>
       </c>
       <c r="H15" t="n">
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L15" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M15" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P15" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="R15" t="n">
         <v>11.9</v>
       </c>
       <c r="S15" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T15" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>13</v>
@@ -3090,22 +3157,22 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,13 +3187,13 @@
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ15" t="n">
         <v>5</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
         <v>24</v>
@@ -3138,46 +3205,46 @@
         <v>20</v>
       </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ15" t="n">
         <v>21</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
         <v>5</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX15" t="n">
         <v>19</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB15" t="n">
         <v>18</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>17</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3326,7 +3393,7 @@
         <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
         <v>19</v>
@@ -3335,7 +3402,7 @@
         <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE18" t="n">
         <v>13</v>
@@ -3663,7 +3730,7 @@
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI18" t="n">
         <v>14</v>
@@ -3690,10 +3757,10 @@
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS18" t="n">
         <v>25</v>
@@ -3711,7 +3778,7 @@
         <v>3</v>
       </c>
       <c r="AX18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
         <v>12</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-7.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3854,7 +3921,7 @@
         <v>11</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3875,7 +3942,7 @@
         <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="n">
         <v>29</v>
@@ -3896,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="AY19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ19" t="n">
         <v>11</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F20" t="n">
         <v>27</v>
       </c>
       <c r="G20" t="n">
-        <v>0.518</v>
+        <v>0.526</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
@@ -3955,88 +4022,88 @@
         <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>83.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L20" t="n">
         <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O20" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.77</v>
+        <v>0.763</v>
       </c>
       <c r="R20" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="S20" t="n">
         <v>31.9</v>
       </c>
       <c r="T20" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="U20" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V20" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="W20" t="n">
         <v>6.9</v>
       </c>
       <c r="X20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
         <v>18.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
         <v>99.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
         <v>15</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK20" t="n">
         <v>13</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>22</v>
@@ -4045,25 +4112,25 @@
         <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
         <v>14</v>
       </c>
       <c r="AP20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS20" t="n">
         <v>18</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AT20" t="n">
         <v>10</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>15</v>
       </c>
       <c r="AU20" t="n">
         <v>15</v>
@@ -4075,10 +4142,10 @@
         <v>26</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ20" t="n">
         <v>6</v>
@@ -4087,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4218,7 +4285,7 @@
         <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
         <v>18</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>30</v>
@@ -4251,7 +4318,7 @@
         <v>16</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E22" t="n">
         <v>32</v>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>0.552</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,10 +4386,10 @@
         <v>38</v>
       </c>
       <c r="J22" t="n">
-        <v>85.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.443</v>
+        <v>0.445</v>
       </c>
       <c r="L22" t="n">
         <v>7.4</v>
@@ -4334,13 +4401,13 @@
         <v>0.327</v>
       </c>
       <c r="O22" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P22" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.759</v>
+        <v>0.756</v>
       </c>
       <c r="R22" t="n">
         <v>12.3</v>
@@ -4352,10 +4419,10 @@
         <v>47.4</v>
       </c>
       <c r="U22" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V22" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W22" t="n">
         <v>7.3</v>
@@ -4364,31 +4431,31 @@
         <v>6.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z22" t="n">
         <v>22.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>101.5</v>
+        <v>101.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
       </c>
       <c r="AF22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
         <v>15</v>
@@ -4400,7 +4467,7 @@
         <v>8</v>
       </c>
       <c r="AK22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL22" t="n">
         <v>16</v>
@@ -4412,7 +4479,7 @@
         <v>25</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP22" t="n">
         <v>11</v>
@@ -4421,7 +4488,7 @@
         <v>16</v>
       </c>
       <c r="AR22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS22" t="n">
         <v>1</v>
@@ -4439,16 +4506,16 @@
         <v>19</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
         <v>26</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G23" t="n">
-        <v>0.328</v>
+        <v>0.322</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
         <v>0.352</v>
@@ -4522,31 +4589,31 @@
         <v>19.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="R23" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>40.7</v>
+        <v>40.9</v>
       </c>
       <c r="U23" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V23" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
         <v>21.3</v>
@@ -4555,13 +4622,13 @@
         <v>18.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.3</v>
+        <v>-5.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4582,7 +4649,7 @@
         <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>23</v>
@@ -4600,19 +4667,19 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR23" t="n">
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV23" t="n">
         <v>22</v>
@@ -4624,7 +4691,7 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4803,16 +4870,16 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
         <v>22</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F25" t="n">
         <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>0.525</v>
+        <v>0.517</v>
       </c>
       <c r="H25" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I25" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="J25" t="n">
-        <v>86.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L25" t="n">
         <v>9.5</v>
@@ -4880,22 +4947,22 @@
         <v>0.358</v>
       </c>
       <c r="O25" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P25" t="n">
         <v>21.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.776</v>
+        <v>0.78</v>
       </c>
       <c r="R25" t="n">
         <v>11</v>
       </c>
       <c r="S25" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="T25" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U25" t="n">
         <v>20.8</v>
@@ -4907,7 +4974,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
         <v>4</v>
@@ -4916,16 +4983,16 @@
         <v>22.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>106.3</v>
+        <v>106.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4934,10 +5001,10 @@
         <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AI25" t="n">
         <v>2</v>
@@ -4955,16 +5022,16 @@
         <v>5</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR25" t="n">
         <v>14</v>
@@ -4973,7 +5040,7 @@
         <v>17</v>
       </c>
       <c r="AT25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU25" t="n">
         <v>20</v>
@@ -4985,7 +5052,7 @@
         <v>5</v>
       </c>
       <c r="AX25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
         <v>6</v>
@@ -5116,19 +5183,19 @@
         <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
         <v>9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5167,7 +5234,7 @@
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY26" t="n">
         <v>4</v>
@@ -5182,7 +5249,7 @@
         <v>9</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5301,7 +5368,7 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5328,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS27" t="n">
         <v>5</v>
@@ -5355,7 +5422,7 @@
         <v>30</v>
       </c>
       <c r="AZ27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E28" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
         <v>23</v>
       </c>
       <c r="G28" t="n">
-        <v>0.589</v>
+        <v>0.596</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,43 +5478,43 @@
         <v>37.9</v>
       </c>
       <c r="J28" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="N28" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="O28" t="n">
         <v>16.4</v>
       </c>
       <c r="P28" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R28" t="n">
         <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T28" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W28" t="n">
         <v>7.6</v>
@@ -5468,10 +5535,10 @@
         <v>100.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5483,16 +5550,16 @@
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,16 +5568,16 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>24</v>
@@ -5519,13 +5586,13 @@
         <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>4.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
         <v>6</v>
@@ -5665,7 +5732,7 @@
         <v>7</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
         <v>8</v>
@@ -5674,7 +5741,7 @@
         <v>13</v>
       </c>
       <c r="AK29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5695,7 +5762,7 @@
         <v>3</v>
       </c>
       <c r="AR29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS29" t="n">
         <v>26</v>
@@ -5719,7 +5786,7 @@
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA29" t="n">
         <v>7</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-1.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -5868,7 +5935,7 @@
         <v>17</v>
       </c>
       <c r="AO30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
@@ -5895,7 +5962,7 @@
         <v>23</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>18</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
@@ -6017,10 +6084,10 @@
         <v>0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF31" t="n">
         <v>12</v>
@@ -6029,7 +6096,7 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6083,10 +6150,10 @@
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-26-2014-15</t>
+          <t>2015-02-26</t>
         </is>
       </c>
     </row>
